--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_362_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_362_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
         <v>4</v>
@@ -2119,16 +2119,16 @@
         <v>24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>5</v>
@@ -2315,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>73</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>19</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4684,7 +4684,7 @@
         <v>18</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
         <v>6</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>88</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>16</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_362_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_362_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>56.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
@@ -851,20 +851,20 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1772,25 +1772,25 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -1935,14 +1935,14 @@
         <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,14 +2131,14 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -3503,14 +3503,14 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4533,25 +4533,25 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5872,14 +5872,14 @@
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y48" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
